--- a/bic_without_vs_with_sunscreen_adjustment.xlsx
+++ b/bic_without_vs_with_sunscreen_adjustment.xlsx
@@ -1,13 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vynguyen/Dropbox/Mac/Documents/GitHub/weight_perception_bp3/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEC26F1-AD3A-1847-9C0C-8ABAC57F4D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="tidy" r:id="rId3" sheetId="1"/>
+    <sheet name="tidy" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tidy!$A$1:$AB$33</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -197,21 +221,21 @@
     <t>Non-Hispanic Asian</t>
   </si>
   <si>
+    <t>Other Hispanic</t>
+  </si>
+  <si>
+    <t>Mexican American</t>
+  </si>
+  <si>
+    <t>Non-Hispanic Black</t>
+  </si>
+  <si>
+    <t>Non-Hispanic White</t>
+  </si>
+  <si>
     <t>All NHANES Women</t>
   </si>
   <si>
-    <t>Non-Hispanic White</t>
-  </si>
-  <si>
-    <t>Other Hispanic</t>
-  </si>
-  <si>
-    <t>Non-Hispanic Black</t>
-  </si>
-  <si>
-    <t>Mexican American</t>
-  </si>
-  <si>
     <t>separate</t>
   </si>
   <si>
@@ -239,21 +263,21 @@
     <t>log10(URXBP3) ~ weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + sunscreen_usage_ordinal</t>
   </si>
   <si>
+    <t>log10(URXBP3) ~ race_weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + sunscreen_usage_ordinal</t>
+  </si>
+  <si>
     <t>log10(URXBP3) ~ race + weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + sunscreen_usage_ordinal</t>
   </si>
   <si>
-    <t>log10(URXBP3) ~ race_weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + sunscreen_usage_ordinal</t>
-  </si>
-  <si>
     <t>log10(URXBP3) ~ weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + INDFMPIR + sunscreen_usage_ordinal</t>
   </si>
   <si>
+    <t>log10(URXBP3) ~ race_weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + INDFMPIR + sunscreen_usage_ordinal</t>
+  </si>
+  <si>
     <t>log10(URXBP3) ~ race + weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + INDFMPIR + sunscreen_usage_ordinal</t>
   </si>
   <si>
-    <t>log10(URXBP3) ~ race_weight_perception + RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + INDFMPIR + sunscreen_usage_ordinal</t>
-  </si>
-  <si>
     <t>RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + sunscreen_usage_ordinal</t>
   </si>
   <si>
@@ -266,21 +290,21 @@
     <t>5.8%</t>
   </si>
   <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>3.4%</t>
+  </si>
+  <si>
     <t>4.1%</t>
   </si>
   <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
     <t>64.6%</t>
   </si>
   <si>
@@ -290,33 +314,33 @@
     <t>10.9%</t>
   </si>
   <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>11.4%</t>
+  </si>
+  <si>
     <t>11.2%</t>
   </si>
   <si>
-    <t>11.4%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
     <t>4.7%</t>
   </si>
   <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
     <t>2.3%</t>
   </si>
   <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
     <t>58.6%</t>
   </si>
   <si>
@@ -326,39 +350,39 @@
     <t>11.7%</t>
   </si>
   <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>8%</t>
+  </si>
+  <si>
+    <t>6.6%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
+  </si>
+  <si>
     <t>8.2%</t>
   </si>
   <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
     <t>3.8%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
     <t>1.7%</t>
   </si>
   <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
     <t>7.5%</t>
   </si>
   <si>
@@ -368,39 +392,39 @@
     <t>10.2%</t>
   </si>
   <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>4.6%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
     <t>5%</t>
   </si>
   <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
     <t>0.5%</t>
   </si>
   <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-  <si>
     <t>17.9%</t>
   </si>
   <si>
@@ -410,36 +434,36 @@
     <t>7.4%</t>
   </si>
   <si>
+    <t>1.9%</t>
+  </si>
+  <si>
     <t>8.5%</t>
   </si>
   <si>
-    <t>1.9%</t>
-  </si>
-  <si>
     <t>90.5%</t>
   </si>
   <si>
     <t>93.8%</t>
   </si>
   <si>
+    <t>95.2%</t>
+  </si>
+  <si>
+    <t>97.2%</t>
+  </si>
+  <si>
+    <t>96.6%</t>
+  </si>
+  <si>
+    <t>95.1%</t>
+  </si>
+  <si>
+    <t>94.4%</t>
+  </si>
+  <si>
     <t>94.2%</t>
   </si>
   <si>
-    <t>94.4%</t>
-  </si>
-  <si>
-    <t>95.1%</t>
-  </si>
-  <si>
-    <t>95.2%</t>
-  </si>
-  <si>
-    <t>96.6%</t>
-  </si>
-  <si>
-    <t>97.2%</t>
-  </si>
-  <si>
     <t>42.8%</t>
   </si>
   <si>
@@ -449,36 +473,36 @@
     <t>78.9%</t>
   </si>
   <si>
+    <t>87.9%</t>
+  </si>
+  <si>
+    <t>89.5%</t>
+  </si>
+  <si>
+    <t>85%</t>
+  </si>
+  <si>
+    <t>84.6%</t>
+  </si>
+  <si>
     <t>83.8%</t>
   </si>
   <si>
-    <t>84.6%</t>
-  </si>
-  <si>
-    <t>85%</t>
-  </si>
-  <si>
-    <t>87.9%</t>
-  </si>
-  <si>
-    <t>89.5%</t>
-  </si>
-  <si>
     <t>89%</t>
   </si>
   <si>
+    <t>95.9%</t>
+  </si>
+  <si>
+    <t>97.6%</t>
+  </si>
+  <si>
+    <t>96.7%</t>
+  </si>
+  <si>
     <t>94.1%</t>
   </si>
   <si>
-    <t>95.9%</t>
-  </si>
-  <si>
-    <t>96.7%</t>
-  </si>
-  <si>
-    <t>97.6%</t>
-  </si>
-  <si>
     <t>23.5%</t>
   </si>
   <si>
@@ -488,29 +512,28 @@
     <t>80.9%</t>
   </si>
   <si>
+    <t>89.4%</t>
+  </si>
+  <si>
+    <t>90.1%</t>
+  </si>
+  <si>
+    <t>82.9%</t>
+  </si>
+  <si>
+    <t>83.1%</t>
+  </si>
+  <si>
     <t>82.4%</t>
-  </si>
-  <si>
-    <t>82.9%</t>
-  </si>
-  <si>
-    <t>83.1%</t>
-  </si>
-  <si>
-    <t>89.4%</t>
-  </si>
-  <si>
-    <t>90.1%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -522,7 +545,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -540,16 +563,331 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AB33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="28.5" customWidth="1"/>
+    <col min="6" max="6" width="79.1640625" customWidth="1"/>
+    <col min="13" max="13" width="73.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -642,10 +980,10 @@
       <c r="C2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" t="n">
-        <v>531.6907334720852</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>531.69073347208518</v>
+      </c>
+      <c r="E2">
         <v>468.9617970563844</v>
       </c>
       <c r="F2" t="s">
@@ -660,11 +998,11 @@
       <c r="I2" t="s">
         <v>73</v>
       </c>
-      <c r="J2" t="n">
-        <v>62.72893641570079</v>
-      </c>
-      <c r="K2" t="n">
-        <v>513.8799672736432</v>
+      <c r="J2">
+        <v>62.728936415700787</v>
+      </c>
+      <c r="K2">
+        <v>513.87996727364316</v>
       </c>
       <c r="L2" t="s">
         <v>74</v>
@@ -672,53 +1010,53 @@
       <c r="M2" t="s">
         <v>80</v>
       </c>
-      <c r="N2" t="n">
-        <v>168.0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="N2">
+        <v>168</v>
+      </c>
+      <c r="O2">
+        <v>7</v>
+      </c>
+      <c r="P2">
+        <v>8</v>
+      </c>
+      <c r="Q2">
         <v>40.99171183522607</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>472.8882554384171</v>
       </c>
       <c r="S2" t="s">
         <v>82</v>
       </c>
-      <c r="T2" t="n">
-        <v>500.3262652642348</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="T2">
+        <v>500.32626526423479</v>
+      </c>
+      <c r="U2">
         <v>17.810766198442025</v>
       </c>
       <c r="V2" t="s">
         <v>109</v>
       </c>
-      <c r="W2" t="n">
-        <v>522.7853503728642</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="W2">
+        <v>522.78535037286417</v>
+      </c>
+      <c r="X2">
         <v>427.97008522115834</v>
       </c>
       <c r="Y2" t="s">
         <v>134</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2">
         <v>254.97675444580523</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2">
         <v>107.53275895250542</v>
       </c>
       <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -728,11 +1066,11 @@
       <c r="C3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" t="n">
-        <v>590.6185315233558</v>
-      </c>
-      <c r="E3" t="n">
-        <v>558.5241473421435</v>
+      <c r="D3">
+        <v>590.61853152335584</v>
+      </c>
+      <c r="E3">
+        <v>558.52414734214346</v>
       </c>
       <c r="F3" t="s">
         <v>68</v>
@@ -746,11 +1084,11 @@
       <c r="I3" t="s">
         <v>73</v>
       </c>
-      <c r="J3" t="n">
-        <v>32.09438418121238</v>
-      </c>
-      <c r="K3" t="n">
-        <v>592.7842272983826</v>
+      <c r="J3">
+        <v>32.094384181212376</v>
+      </c>
+      <c r="K3">
+        <v>592.78422729838258</v>
       </c>
       <c r="L3" t="s">
         <v>74</v>
@@ -758,53 +1096,53 @@
       <c r="M3" t="s">
         <v>80</v>
       </c>
-      <c r="N3" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>42.77686024573975</v>
-      </c>
-      <c r="R3" t="n">
-        <v>550.0073670526428</v>
+      <c r="N3">
+        <v>210</v>
+      </c>
+      <c r="O3">
+        <v>7</v>
+      </c>
+      <c r="P3">
+        <v>8</v>
+      </c>
+      <c r="Q3">
+        <v>42.776860245739748</v>
+      </c>
+      <c r="R3">
+        <v>550.00736705264285</v>
       </c>
       <c r="S3" t="s">
         <v>83</v>
       </c>
-      <c r="T3" t="n">
-        <v>574.5713394327497</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.165695775026734</v>
+      <c r="T3">
+        <v>574.57133943274971</v>
+      </c>
+      <c r="U3">
+        <v>2.1656957750267338</v>
       </c>
       <c r="V3" t="s">
         <v>110</v>
       </c>
-      <c r="W3" t="n">
-        <v>591.7013794108692</v>
-      </c>
-      <c r="X3" t="n">
-        <v>515.7472870964037</v>
+      <c r="W3">
+        <v>591.70137941086921</v>
+      </c>
+      <c r="X3">
+        <v>515.74728709640374</v>
       </c>
       <c r="Y3" t="s">
         <v>135</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3">
         <v>300.6505037939416</v>
       </c>
-      <c r="AA3" t="n">
-        <v>100.0</v>
+      <c r="AA3">
+        <v>100</v>
       </c>
       <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -814,11 +1152,11 @@
       <c r="C4" t="s">
         <v>66</v>
       </c>
-      <c r="D4" t="n">
-        <v>9508.406183620044</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9112.019807815464</v>
+      <c r="D4">
+        <v>794.60203568505938</v>
+      </c>
+      <c r="E4">
+        <v>764.82338428568096</v>
       </c>
       <c r="F4" t="s">
         <v>68</v>
@@ -832,79 +1170,79 @@
       <c r="I4" t="s">
         <v>73</v>
       </c>
-      <c r="J4" t="n">
-        <v>396.3863758045791</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9668.528734572054</v>
+      <c r="J4">
+        <v>29.778651399378418</v>
+      </c>
+      <c r="K4">
+        <v>800.86537368618792</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M4" t="s">
         <v>80</v>
       </c>
-      <c r="N4" t="n">
-        <v>3517.0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>106.14972722216176</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9562.379007349891</v>
+      <c r="N4">
+        <v>289</v>
+      </c>
+      <c r="O4">
+        <v>7</v>
+      </c>
+      <c r="P4">
+        <v>8</v>
+      </c>
+      <c r="Q4">
+        <v>45.331413504899459</v>
+      </c>
+      <c r="R4">
+        <v>755.53396018128842</v>
       </c>
       <c r="S4" t="s">
         <v>84</v>
       </c>
-      <c r="T4" t="n">
-        <v>9310.212995717753</v>
-      </c>
-      <c r="U4" t="n">
-        <v>160.12255095201</v>
+      <c r="T4">
+        <v>779.71270998537011</v>
+      </c>
+      <c r="U4">
+        <v>6.2633380011285453</v>
       </c>
       <c r="V4" t="s">
         <v>111</v>
       </c>
-      <c r="W4" t="n">
-        <v>9588.46745909605</v>
-      </c>
-      <c r="X4" t="n">
-        <v>9005.870080593302</v>
+      <c r="W4">
+        <v>797.73370468562371</v>
+      </c>
+      <c r="X4">
+        <v>719.49197078078146</v>
       </c>
       <c r="Y4" t="s">
         <v>136</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4609.084767518813</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>100.0</v>
+      <c r="Z4">
+        <v>405.07739889529023</v>
+      </c>
+      <c r="AA4">
+        <v>100</v>
       </c>
       <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9529.314117124317</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9138.573019016078</v>
+        <v>66</v>
+      </c>
+      <c r="D5">
+        <v>1541.0214847036707</v>
+      </c>
+      <c r="E5">
+        <v>1504.0099582022199</v>
       </c>
       <c r="F5" t="s">
         <v>68</v>
@@ -918,79 +1256,79 @@
       <c r="I5" t="s">
         <v>73</v>
       </c>
-      <c r="J5" t="n">
-        <v>390.7410981082394</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9668.528734572054</v>
+      <c r="J5">
+        <v>37.011526501450817</v>
+      </c>
+      <c r="K5">
+        <v>1546.3354147349769</v>
       </c>
       <c r="L5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M5" t="s">
         <v>80</v>
       </c>
-      <c r="N5" t="n">
-        <v>3517.0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>138.81118175205768</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9529.717552819995</v>
+      <c r="N5">
+        <v>570</v>
+      </c>
+      <c r="O5">
+        <v>7</v>
+      </c>
+      <c r="P5">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>50.765090886628769</v>
+      </c>
+      <c r="R5">
+        <v>1495.5703238483482</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9333.943568070197</v>
-      </c>
-      <c r="U5" t="n">
-        <v>139.2146174477366</v>
+        <v>85</v>
+      </c>
+      <c r="T5">
+        <v>1522.5157214529454</v>
+      </c>
+      <c r="U5">
+        <v>5.3139300313061995</v>
       </c>
       <c r="V5" t="s">
-        <v>112</v>
-      </c>
-      <c r="W5" t="n">
-        <v>9598.921425848184</v>
-      </c>
-      <c r="X5" t="n">
-        <v>8999.761837264019</v>
+        <v>110</v>
+      </c>
+      <c r="W5">
+        <v>1543.6784497193239</v>
+      </c>
+      <c r="X5">
+        <v>1453.2448673155911</v>
       </c>
       <c r="Y5" t="s">
         <v>137</v>
       </c>
-      <c r="Z5" t="n">
-        <v>4638.692100384068</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>100.0</v>
+      <c r="Z5">
+        <v>777.38752454442431</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
       </c>
       <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>66</v>
       </c>
-      <c r="D6" t="n">
-        <v>4004.762689280187</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3867.744612330402</v>
+      <c r="D6">
+        <v>2137.4400458917889</v>
+      </c>
+      <c r="E6">
+        <v>2068.6686736844122</v>
       </c>
       <c r="F6" t="s">
         <v>68</v>
@@ -1004,11 +1342,11 @@
       <c r="I6" t="s">
         <v>73</v>
       </c>
-      <c r="J6" t="n">
-        <v>137.0180769497847</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4065.2240051185613</v>
+      <c r="J6">
+        <v>68.771372207376771</v>
+      </c>
+      <c r="K6">
+        <v>2139.8094378473497</v>
       </c>
       <c r="L6" t="s">
         <v>74</v>
@@ -1016,67 +1354,67 @@
       <c r="M6" t="s">
         <v>80</v>
       </c>
-      <c r="N6" t="n">
-        <v>1470.0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>58.344141438182255</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4006.879863680379</v>
+      <c r="N6">
+        <v>810</v>
+      </c>
+      <c r="O6">
+        <v>7</v>
+      </c>
+      <c r="P6">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>53.576273981331873</v>
+      </c>
+      <c r="R6">
+        <v>2086.233163866018</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3936.2536508052945</v>
-      </c>
-      <c r="U6" t="n">
-        <v>60.4613158383745</v>
+        <v>86</v>
+      </c>
+      <c r="T6">
+        <v>2103.0543597881006</v>
+      </c>
+      <c r="U6">
+        <v>2.3693919555607863</v>
       </c>
       <c r="V6" t="s">
         <v>112</v>
       </c>
-      <c r="W6" t="n">
-        <v>4034.993347199374</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3809.40047089222</v>
+      <c r="W6">
+        <v>2138.6247418695693</v>
+      </c>
+      <c r="X6">
+        <v>2015.0923997030802</v>
       </c>
       <c r="Y6" t="s">
         <v>138</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1963.0443768842922</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>100.0</v>
+      <c r="Z6">
+        <v>1061.1224738328719</v>
+      </c>
+      <c r="AA6">
+        <v>100</v>
       </c>
       <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
-      <c r="D7" t="n">
-        <v>794.6020356850594</v>
-      </c>
-      <c r="E7" t="n">
-        <v>764.823384285681</v>
+      <c r="D7">
+        <v>4004.7626892801868</v>
+      </c>
+      <c r="E7">
+        <v>3867.7446123304021</v>
       </c>
       <c r="F7" t="s">
         <v>68</v>
@@ -1090,11 +1428,11 @@
       <c r="I7" t="s">
         <v>73</v>
       </c>
-      <c r="J7" t="n">
-        <v>29.77865139937842</v>
-      </c>
-      <c r="K7" t="n">
-        <v>800.8653736861879</v>
+      <c r="J7">
+        <v>137.0180769497847</v>
+      </c>
+      <c r="K7">
+        <v>4065.2240051185613</v>
       </c>
       <c r="L7" t="s">
         <v>74</v>
@@ -1102,67 +1440,67 @@
       <c r="M7" t="s">
         <v>80</v>
       </c>
-      <c r="N7" t="n">
-        <v>289.0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>45.33141350489946</v>
-      </c>
-      <c r="R7" t="n">
-        <v>755.5339601812884</v>
+      <c r="N7">
+        <v>1470</v>
+      </c>
+      <c r="O7">
+        <v>7</v>
+      </c>
+      <c r="P7">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>58.344141438182255</v>
+      </c>
+      <c r="R7">
+        <v>4006.879863680379</v>
       </c>
       <c r="S7" t="s">
-        <v>86</v>
-      </c>
-      <c r="T7" t="n">
-        <v>779.7127099853701</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6.263338001128545</v>
+        <v>87</v>
+      </c>
+      <c r="T7">
+        <v>3936.2536508052945</v>
+      </c>
+      <c r="U7">
+        <v>60.461315838374503</v>
       </c>
       <c r="V7" t="s">
         <v>113</v>
       </c>
-      <c r="W7" t="n">
-        <v>797.7337046856237</v>
-      </c>
-      <c r="X7" t="n">
-        <v>719.4919707807815</v>
+      <c r="W7">
+        <v>4034.9933471993741</v>
+      </c>
+      <c r="X7">
+        <v>3809.4004708922198</v>
       </c>
       <c r="Y7" t="s">
         <v>139</v>
       </c>
-      <c r="Z7" t="n">
-        <v>405.07739889529023</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>100.0</v>
+      <c r="Z7">
+        <v>1963.0443768842922</v>
+      </c>
+      <c r="AA7">
+        <v>100</v>
       </c>
       <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2137.440045891789</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2068.668673684412</v>
+        <v>67</v>
+      </c>
+      <c r="D8">
+        <v>9529.3141171243169</v>
+      </c>
+      <c r="E8">
+        <v>9138.5730190160775</v>
       </c>
       <c r="F8" t="s">
         <v>68</v>
@@ -1176,65 +1514,65 @@
       <c r="I8" t="s">
         <v>73</v>
       </c>
-      <c r="J8" t="n">
-        <v>68.77137220737677</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2139.8094378473497</v>
+      <c r="J8">
+        <v>390.74109810823938</v>
+      </c>
+      <c r="K8">
+        <v>9668.5287345720535</v>
       </c>
       <c r="L8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M8" t="s">
         <v>80</v>
       </c>
-      <c r="N8" t="n">
-        <v>810.0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>53.57627398133187</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2086.233163866018</v>
+      <c r="N8">
+        <v>3517</v>
+      </c>
+      <c r="O8">
+        <v>16</v>
+      </c>
+      <c r="P8">
+        <v>17</v>
+      </c>
+      <c r="Q8">
+        <v>138.81118175205768</v>
+      </c>
+      <c r="R8">
+        <v>9529.717552819995</v>
       </c>
       <c r="S8" t="s">
-        <v>87</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2103.0543597881006</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.3693919555607863</v>
+        <v>88</v>
+      </c>
+      <c r="T8">
+        <v>9333.9435680701972</v>
+      </c>
+      <c r="U8">
+        <v>139.2146174477366</v>
       </c>
       <c r="V8" t="s">
-        <v>114</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2138.6247418695693</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2015.0923997030802</v>
+        <v>113</v>
+      </c>
+      <c r="W8">
+        <v>9598.9214258481843</v>
+      </c>
+      <c r="X8">
+        <v>8999.7618372640191</v>
       </c>
       <c r="Y8" t="s">
         <v>140</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1061.122473832872</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>100.0</v>
+      <c r="Z8">
+        <v>4638.692100384068</v>
+      </c>
+      <c r="AA8">
+        <v>100</v>
       </c>
       <c r="AB8" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1244,11 +1582,11 @@
       <c r="C9" t="s">
         <v>66</v>
       </c>
-      <c r="D9" t="n">
-        <v>1541.0214847036707</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1504.0099582022199</v>
+      <c r="D9">
+        <v>9508.4061836200435</v>
+      </c>
+      <c r="E9">
+        <v>9112.0198078154644</v>
       </c>
       <c r="F9" t="s">
         <v>68</v>
@@ -1262,65 +1600,65 @@
       <c r="I9" t="s">
         <v>73</v>
       </c>
-      <c r="J9" t="n">
-        <v>37.01152650145082</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1546.335414734977</v>
+      <c r="J9">
+        <v>396.38637580457907</v>
+      </c>
+      <c r="K9">
+        <v>9668.5287345720535</v>
       </c>
       <c r="L9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M9" t="s">
         <v>80</v>
       </c>
-      <c r="N9" t="n">
-        <v>570.0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>50.76509088662877</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1495.5703238483482</v>
+      <c r="N9">
+        <v>3517</v>
+      </c>
+      <c r="O9">
+        <v>12</v>
+      </c>
+      <c r="P9">
+        <v>13</v>
+      </c>
+      <c r="Q9">
+        <v>106.14972722216176</v>
+      </c>
+      <c r="R9">
+        <v>9562.3790073498913</v>
       </c>
       <c r="S9" t="s">
         <v>88</v>
       </c>
-      <c r="T9" t="n">
-        <v>1522.5157214529454</v>
-      </c>
-      <c r="U9" t="n">
-        <v>5.3139300313061995</v>
+      <c r="T9">
+        <v>9310.2129957177531</v>
+      </c>
+      <c r="U9">
+        <v>160.12255095200999</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1543.678449719324</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1453.2448673155911</v>
+        <v>114</v>
+      </c>
+      <c r="W9">
+        <v>9588.4674590960494</v>
+      </c>
+      <c r="X9">
+        <v>9005.8700805933022</v>
       </c>
       <c r="Y9" t="s">
         <v>141</v>
       </c>
-      <c r="Z9" t="n">
-        <v>777.3875245444243</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>100.0</v>
+      <c r="Z9">
+        <v>4609.0847675188134</v>
+      </c>
+      <c r="AA9">
+        <v>100</v>
       </c>
       <c r="AB9" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1330,10 +1668,10 @@
       <c r="C10" t="s">
         <v>66</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>193.47815883277184</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>149.66005144689746</v>
       </c>
       <c r="F10" t="s">
@@ -1348,11 +1686,11 @@
       <c r="I10" t="s">
         <v>73</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>43.818107385874384</v>
       </c>
-      <c r="K10" t="n">
-        <v>188.4136720396013</v>
+      <c r="K10">
+        <v>188.41367203960129</v>
       </c>
       <c r="L10" t="s">
         <v>74</v>
@@ -1360,53 +1698,53 @@
       <c r="M10" t="s">
         <v>80</v>
       </c>
-      <c r="N10" t="n">
-        <v>146.0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N10">
+        <v>146</v>
+      </c>
+      <c r="O10">
+        <v>7</v>
+      </c>
+      <c r="P10">
+        <v>8</v>
+      </c>
+      <c r="Q10">
         <v>120.61771315997485</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10">
         <v>67.79595887962644</v>
       </c>
       <c r="S10" t="s">
         <v>89</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10">
         <v>171.56910513983465</v>
       </c>
-      <c r="U10" t="n">
-        <v>5.064486793170545</v>
+      <c r="U10">
+        <v>5.0644867931705448</v>
       </c>
       <c r="V10" t="s">
         <v>115</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W10">
         <v>190.94591543618657</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10">
         <v>29.0423382869226</v>
       </c>
       <c r="Y10" t="s">
         <v>142</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10">
         <v>135.13888230343616</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10">
         <v>114.94037956499052</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB10">
         <v>3531432.4683565227</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1416,11 +1754,11 @@
       <c r="C11" t="s">
         <v>66</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>200.5707227602619</v>
       </c>
-      <c r="E11" t="n">
-        <v>178.8571712077849</v>
+      <c r="E11">
+        <v>178.85717120778489</v>
       </c>
       <c r="F11" t="s">
         <v>68</v>
@@ -1434,10 +1772,10 @@
       <c r="I11" t="s">
         <v>73</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>21.713551552477014</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>207.09546233829298</v>
       </c>
       <c r="L11" t="s">
@@ -1446,66 +1784,66 @@
       <c r="M11" t="s">
         <v>80</v>
       </c>
-      <c r="N11" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N11">
+        <v>210</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
+      </c>
+      <c r="P11">
+        <v>8</v>
+      </c>
+      <c r="Q11">
         <v>116.39862738583389</v>
       </c>
-      <c r="R11" t="n">
-        <v>90.69683495245908</v>
+      <c r="R11">
+        <v>90.696834952459085</v>
       </c>
       <c r="S11" t="s">
         <v>90</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11">
         <v>189.71394698402338</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11">
         <v>6.524739578031074</v>
       </c>
       <c r="V11" t="s">
         <v>116</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W11">
         <v>203.83309254927744</v>
       </c>
-      <c r="X11" t="n">
-        <v>62.458543821951</v>
+      <c r="X11">
+        <v>62.458543821950997</v>
       </c>
       <c r="Y11" t="s">
         <v>143</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11">
         <v>147.6278992968094</v>
       </c>
-      <c r="AA11" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AA11">
+        <v>100</v>
+      </c>
+      <c r="AB11">
         <v>2084059.897883856</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
         <v>66</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>242.19216920080373</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>227.69657289196857</v>
       </c>
       <c r="F12" t="s">
@@ -1520,10 +1858,10 @@
       <c r="I12" t="s">
         <v>73</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>14.495596308835161</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>255.81621406346676</v>
       </c>
       <c r="L12" t="s">
@@ -1532,67 +1870,67 @@
       <c r="M12" t="s">
         <v>80</v>
       </c>
-      <c r="N12" t="n">
-        <v>265.0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N12">
+        <v>265</v>
+      </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
+      <c r="P12">
+        <v>8</v>
+      </c>
+      <c r="Q12">
         <v>122.48502674084402</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12">
         <v>133.33118732262272</v>
       </c>
       <c r="S12" t="s">
         <v>91</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12">
         <v>234.94437104638615</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12">
         <v>13.624044862663027</v>
       </c>
       <c r="V12" t="s">
         <v>117</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W12">
         <v>249.00419163213525</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X12">
         <v>105.21154615112455</v>
       </c>
       <c r="Y12" t="s">
         <v>144</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12">
         <v>175.0907998164063</v>
       </c>
-      <c r="AA12" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4459861.825137717</v>
+      <c r="AA12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
+        <v>4459861.8251377167</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
         <v>66</v>
       </c>
-      <c r="D13" t="n">
-        <v>2802.793554098226</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2500.270612231032</v>
+      <c r="D13">
+        <v>413.26464108738156</v>
+      </c>
+      <c r="E13">
+        <v>382.09388276156164</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -1606,79 +1944,79 @@
       <c r="I13" t="s">
         <v>73</v>
       </c>
-      <c r="J13" t="n">
-        <v>302.5229418671943</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2937.5105153151762</v>
+      <c r="J13">
+        <v>31.170758325819918</v>
+      </c>
+      <c r="K13">
+        <v>417.39598867452742</v>
       </c>
       <c r="L13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M13" t="s">
         <v>80</v>
       </c>
-      <c r="N13" t="n">
-        <v>3072.0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>235.44726481081028</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2702.063250504366</v>
+      <c r="N13">
+        <v>479</v>
+      </c>
+      <c r="O13">
+        <v>7</v>
+      </c>
+      <c r="P13">
+        <v>8</v>
+      </c>
+      <c r="Q13">
+        <v>124.99745527457709</v>
+      </c>
+      <c r="R13">
+        <v>292.39853339995034</v>
       </c>
       <c r="S13" t="s">
         <v>92</v>
       </c>
-      <c r="T13" t="n">
-        <v>2651.532083164629</v>
-      </c>
-      <c r="U13" t="n">
-        <v>134.71696121695004</v>
+      <c r="T13">
+        <v>397.67926192447158</v>
+      </c>
+      <c r="U13">
+        <v>4.1313475871458536</v>
       </c>
       <c r="V13" t="s">
         <v>118</v>
       </c>
-      <c r="W13" t="n">
-        <v>2870.152034706701</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2264.8233474202216</v>
+      <c r="W13">
+        <v>415.33031488095446</v>
+      </c>
+      <c r="X13">
+        <v>257.09642748698457</v>
       </c>
       <c r="Y13" t="s">
         <v>145</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1367.8589385209211</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.339218836454763E7</v>
+      <c r="Z13">
+        <v>253.54566901806936</v>
+      </c>
+      <c r="AA13">
+        <v>100</v>
+      </c>
+      <c r="AB13">
+        <v>6105386.11557924</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2832.193813850392</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2532.500021612931</v>
+        <v>66</v>
+      </c>
+      <c r="D14">
+        <v>583.7499815486301</v>
+      </c>
+      <c r="E14">
+        <v>540.63549580898177</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
@@ -1692,78 +2030,78 @@
       <c r="I14" t="s">
         <v>73</v>
       </c>
-      <c r="J14" t="n">
-        <v>299.6937922374609</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2937.5105153151762</v>
+      <c r="J14">
+        <v>43.11448573964833</v>
+      </c>
+      <c r="K14">
+        <v>588.86174422475676</v>
       </c>
       <c r="L14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M14" t="s">
         <v>80</v>
       </c>
-      <c r="N14" t="n">
-        <v>3072.0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>307.89257706029036</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2629.6179382548858</v>
+      <c r="N14">
+        <v>703</v>
+      </c>
+      <c r="O14">
+        <v>7</v>
+      </c>
+      <c r="P14">
+        <v>8</v>
+      </c>
+      <c r="Q14">
+        <v>128.6168977302446</v>
+      </c>
+      <c r="R14">
+        <v>460.24484649451216</v>
       </c>
       <c r="S14" t="s">
         <v>93</v>
       </c>
-      <c r="T14" t="n">
-        <v>2682.3469177316615</v>
-      </c>
-      <c r="U14" t="n">
-        <v>105.31670146478427</v>
+      <c r="T14">
+        <v>562.19273867880588</v>
+      </c>
+      <c r="U14">
+        <v>5.1117626761266592</v>
       </c>
       <c r="V14" t="s">
         <v>119</v>
       </c>
-      <c r="W14" t="n">
-        <v>2884.852164582784</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2224.6074445526406</v>
+      <c r="W14">
+        <v>586.30586288669338</v>
+      </c>
+      <c r="X14">
+        <v>412.01859807873717</v>
       </c>
       <c r="Y14" t="s">
         <v>146</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1420.1962993366108</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.339218836454763E7</v>
+      <c r="Z14">
+        <v>334.62619676961322</v>
+      </c>
+      <c r="AA14">
+        <v>100</v>
+      </c>
+      <c r="AB14">
+        <v>9598450.2995834183</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
         <v>66</v>
       </c>
-      <c r="D15" t="n">
-        <v>1185.606213668051</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15">
+        <v>1185.6062136680509</v>
+      </c>
+      <c r="E15">
         <v>1071.824898662692</v>
       </c>
       <c r="F15" t="s">
@@ -1778,10 +2116,10 @@
       <c r="I15" t="s">
         <v>73</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>113.78131500535892</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>1236.4523942074045</v>
       </c>
       <c r="L15" t="s">
@@ -1790,53 +2128,53 @@
       <c r="M15" t="s">
         <v>80</v>
       </c>
-      <c r="N15" t="n">
-        <v>1269.0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N15">
+        <v>1269</v>
+      </c>
+      <c r="O15">
+        <v>7</v>
+      </c>
+      <c r="P15">
+        <v>8</v>
+      </c>
+      <c r="Q15">
         <v>141.42893075255975</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>1095.0234634548447</v>
       </c>
       <c r="S15" t="s">
         <v>94</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15">
         <v>1128.7155561653715</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15">
         <v>50.846180539353554</v>
       </c>
       <c r="V15" t="s">
         <v>120</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W15">
         <v>1211.0293039377277</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X15">
         <v>930.3959679101323</v>
       </c>
       <c r="Y15" t="s">
         <v>147</v>
       </c>
-      <c r="Z15" t="n">
-        <v>606.6269147076259</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>4.761299775800688E7</v>
+      <c r="Z15">
+        <v>606.62691470762593</v>
+      </c>
+      <c r="AA15">
+        <v>100</v>
+      </c>
+      <c r="AB15">
+        <v>47612997.758006878</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1844,13 +2182,13 @@
         <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="n">
-        <v>413.26464108738156</v>
-      </c>
-      <c r="E16" t="n">
-        <v>382.09388276156164</v>
+        <v>67</v>
+      </c>
+      <c r="D16">
+        <v>2832.193813850392</v>
+      </c>
+      <c r="E16">
+        <v>2532.5000216129311</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
@@ -1864,79 +2202,79 @@
       <c r="I16" t="s">
         <v>73</v>
       </c>
-      <c r="J16" t="n">
-        <v>31.170758325819918</v>
-      </c>
-      <c r="K16" t="n">
-        <v>417.3959886745274</v>
+      <c r="J16">
+        <v>299.69379223746091</v>
+      </c>
+      <c r="K16">
+        <v>2937.5105153151762</v>
       </c>
       <c r="L16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M16" t="s">
         <v>80</v>
       </c>
-      <c r="N16" t="n">
-        <v>479.0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>124.99745527457709</v>
-      </c>
-      <c r="R16" t="n">
-        <v>292.39853339995034</v>
+      <c r="N16">
+        <v>3072</v>
+      </c>
+      <c r="O16">
+        <v>16</v>
+      </c>
+      <c r="P16">
+        <v>17</v>
+      </c>
+      <c r="Q16">
+        <v>307.89257706029036</v>
+      </c>
+      <c r="R16">
+        <v>2629.6179382548858</v>
       </c>
       <c r="S16" t="s">
         <v>95</v>
       </c>
-      <c r="T16" t="n">
-        <v>397.6792619244716</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.131347587145854</v>
+      <c r="T16">
+        <v>2682.3469177316615</v>
+      </c>
+      <c r="U16">
+        <v>105.31670146478427</v>
       </c>
       <c r="V16" t="s">
         <v>121</v>
       </c>
-      <c r="W16" t="n">
-        <v>415.33031488095446</v>
-      </c>
-      <c r="X16" t="n">
-        <v>257.09642748698457</v>
+      <c r="W16">
+        <v>2884.8521645827841</v>
+      </c>
+      <c r="X16">
+        <v>2224.6074445526406</v>
       </c>
       <c r="Y16" t="s">
         <v>148</v>
       </c>
-      <c r="Z16" t="n">
-        <v>253.54566901806936</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>6105386.11557924</v>
+      <c r="Z16">
+        <v>1420.1962993366108</v>
+      </c>
+      <c r="AA16">
+        <v>100</v>
+      </c>
+      <c r="AB16">
+        <v>73392188.364547625</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
         <v>66</v>
       </c>
-      <c r="D17" t="n">
-        <v>583.7499815486301</v>
-      </c>
-      <c r="E17" t="n">
-        <v>540.6354958089818</v>
+      <c r="D17">
+        <v>2802.7935540982262</v>
+      </c>
+      <c r="E17">
+        <v>2500.2706122310319</v>
       </c>
       <c r="F17" t="s">
         <v>68</v>
@@ -1950,65 +2288,65 @@
       <c r="I17" t="s">
         <v>73</v>
       </c>
-      <c r="J17" t="n">
-        <v>43.11448573964833</v>
-      </c>
-      <c r="K17" t="n">
-        <v>588.8617442247568</v>
+      <c r="J17">
+        <v>302.52294186719428</v>
+      </c>
+      <c r="K17">
+        <v>2937.5105153151762</v>
       </c>
       <c r="L17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
         <v>80</v>
       </c>
-      <c r="N17" t="n">
-        <v>703.0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>128.6168977302446</v>
-      </c>
-      <c r="R17" t="n">
-        <v>460.24484649451216</v>
+      <c r="N17">
+        <v>3072</v>
+      </c>
+      <c r="O17">
+        <v>12</v>
+      </c>
+      <c r="P17">
+        <v>13</v>
+      </c>
+      <c r="Q17">
+        <v>235.44726481081028</v>
+      </c>
+      <c r="R17">
+        <v>2702.0632505043659</v>
       </c>
       <c r="S17" t="s">
         <v>96</v>
       </c>
-      <c r="T17" t="n">
-        <v>562.1927386788059</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5.111762676126659</v>
+      <c r="T17">
+        <v>2651.5320831646291</v>
+      </c>
+      <c r="U17">
+        <v>134.71696121695004</v>
       </c>
       <c r="V17" t="s">
         <v>122</v>
       </c>
-      <c r="W17" t="n">
-        <v>586.3058628866934</v>
-      </c>
-      <c r="X17" t="n">
-        <v>412.01859807873717</v>
+      <c r="W17">
+        <v>2870.1520347067012</v>
+      </c>
+      <c r="X17">
+        <v>2264.8233474202216</v>
       </c>
       <c r="Y17" t="s">
         <v>149</v>
       </c>
-      <c r="Z17" t="n">
-        <v>334.6261967696132</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9598450.299583418</v>
+      <c r="Z17">
+        <v>1367.8589385209211</v>
+      </c>
+      <c r="AA17">
+        <v>100</v>
+      </c>
+      <c r="AB17">
+        <v>73392188.364547625</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -2018,11 +2356,11 @@
       <c r="C18" t="s">
         <v>66</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>511.33469453967507</v>
       </c>
-      <c r="E18" t="n">
-        <v>462.5984900123134</v>
+      <c r="E18">
+        <v>462.59849001231339</v>
       </c>
       <c r="F18" t="s">
         <v>69</v>
@@ -2036,11 +2374,11 @@
       <c r="I18" t="s">
         <v>73</v>
       </c>
-      <c r="J18" t="n">
-        <v>48.73620452736168</v>
-      </c>
-      <c r="K18" t="n">
-        <v>513.8799672736432</v>
+      <c r="J18">
+        <v>48.736204527361679</v>
+      </c>
+      <c r="K18">
+        <v>513.87996727364316</v>
       </c>
       <c r="L18" t="s">
         <v>77</v>
@@ -2048,53 +2386,53 @@
       <c r="M18" t="s">
         <v>81</v>
       </c>
-      <c r="N18" t="n">
-        <v>168.0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>46.11567581462933</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="N18">
+        <v>168</v>
+      </c>
+      <c r="O18">
+        <v>8</v>
+      </c>
+      <c r="P18">
+        <v>9</v>
+      </c>
+      <c r="Q18">
+        <v>46.115675814629327</v>
+      </c>
+      <c r="R18">
         <v>467.76429145901386</v>
       </c>
       <c r="S18" t="s">
         <v>94</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18">
         <v>486.96659227599423</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18">
         <v>2.5452727339680905</v>
       </c>
       <c r="V18" t="s">
         <v>123</v>
       </c>
-      <c r="W18" t="n">
-        <v>512.6073309066592</v>
-      </c>
-      <c r="X18" t="n">
-        <v>416.4828141976841</v>
+      <c r="W18">
+        <v>512.60733090665917</v>
+      </c>
+      <c r="X18">
+        <v>416.48281419768409</v>
       </c>
       <c r="Y18" t="s">
         <v>150</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z18">
         <v>254.35708291347134</v>
       </c>
-      <c r="AA18" t="n">
-        <v>100.0</v>
+      <c r="AA18">
+        <v>100</v>
       </c>
       <c r="AB18" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2104,11 +2442,11 @@
       <c r="C19" t="s">
         <v>66</v>
       </c>
-      <c r="D19" t="n">
-        <v>584.4502325341015</v>
-      </c>
-      <c r="E19" t="n">
-        <v>558.8496900624206</v>
+      <c r="D19">
+        <v>584.45023253410147</v>
+      </c>
+      <c r="E19">
+        <v>558.84969006242056</v>
       </c>
       <c r="F19" t="s">
         <v>69</v>
@@ -2122,11 +2460,11 @@
       <c r="I19" t="s">
         <v>73</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>25.60054247168091</v>
       </c>
-      <c r="K19" t="n">
-        <v>592.7842272983826</v>
+      <c r="K19">
+        <v>592.78422729838258</v>
       </c>
       <c r="L19" t="s">
         <v>77</v>
@@ -2134,53 +2472,53 @@
       <c r="M19" t="s">
         <v>81</v>
       </c>
-      <c r="N19" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N19">
+        <v>210</v>
+      </c>
+      <c r="O19">
+        <v>8</v>
+      </c>
+      <c r="P19">
+        <v>9</v>
+      </c>
+      <c r="Q19">
         <v>48.123967776457214</v>
       </c>
-      <c r="R19" t="n">
-        <v>544.6602595219254</v>
+      <c r="R19">
+        <v>544.66025952192535</v>
       </c>
       <c r="S19" t="s">
         <v>97</v>
       </c>
-      <c r="T19" t="n">
-        <v>571.649961298261</v>
-      </c>
-      <c r="U19" t="n">
-        <v>8.333994764281101</v>
+      <c r="T19">
+        <v>571.64996129826102</v>
+      </c>
+      <c r="U19">
+        <v>8.3339947642811012</v>
       </c>
       <c r="V19" t="s">
-        <v>112</v>
-      </c>
-      <c r="W19" t="n">
-        <v>588.617229916242</v>
-      </c>
-      <c r="X19" t="n">
+        <v>113</v>
+      </c>
+      <c r="W19">
+        <v>588.61722991624197</v>
+      </c>
+      <c r="X19">
         <v>510.72572228596334</v>
       </c>
       <c r="Y19" t="s">
         <v>135</v>
       </c>
-      <c r="Z19" t="n">
-        <v>303.4868289194389</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>100.0</v>
+      <c r="Z19">
+        <v>303.48682891943889</v>
+      </c>
+      <c r="AA19">
+        <v>100</v>
       </c>
       <c r="AB19" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2190,11 +2528,11 @@
       <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="D20" t="n">
-        <v>9397.28785346139</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9080.720575721743</v>
+      <c r="D20">
+        <v>799.27799277194833</v>
+      </c>
+      <c r="E20">
+        <v>770.29479541452952</v>
       </c>
       <c r="F20" t="s">
         <v>69</v>
@@ -2208,79 +2546,79 @@
       <c r="I20" t="s">
         <v>73</v>
       </c>
-      <c r="J20" t="n">
-        <v>316.56727773964667</v>
-      </c>
-      <c r="K20" t="n">
-        <v>9668.528734572054</v>
+      <c r="J20">
+        <v>28.983197357418817</v>
+      </c>
+      <c r="K20">
+        <v>800.86537368618792</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M20" t="s">
         <v>81</v>
       </c>
-      <c r="N20" t="n">
-        <v>3517.0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>114.31509085463574</v>
-      </c>
-      <c r="R20" t="n">
-        <v>9554.213643717418</v>
+      <c r="N20">
+        <v>289</v>
+      </c>
+      <c r="O20">
+        <v>8</v>
+      </c>
+      <c r="P20">
+        <v>9</v>
+      </c>
+      <c r="Q20">
+        <v>50.997840193011889</v>
+      </c>
+      <c r="R20">
+        <v>749.86753349317598</v>
       </c>
       <c r="S20" t="s">
-        <v>87</v>
-      </c>
-      <c r="T20" t="n">
-        <v>9239.004214591567</v>
-      </c>
-      <c r="U20" t="n">
-        <v>271.2408811106634</v>
+        <v>84</v>
+      </c>
+      <c r="T20">
+        <v>784.78639409323887</v>
+      </c>
+      <c r="U20">
+        <v>1.5873809142395885</v>
       </c>
       <c r="V20" t="s">
         <v>124</v>
       </c>
-      <c r="W20" t="n">
-        <v>9532.90829401672</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8966.405484867108</v>
+      <c r="W20">
+        <v>800.07168322906819</v>
+      </c>
+      <c r="X20">
+        <v>719.29695522151758</v>
       </c>
       <c r="Y20" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4597.51783328819</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>100.0</v>
+        <v>151</v>
+      </c>
+      <c r="Z20">
+        <v>410.64631780377073</v>
+      </c>
+      <c r="AA20">
+        <v>100</v>
       </c>
       <c r="AB20" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="n">
-        <v>9420.120496478445</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9107.75707397262</v>
+        <v>66</v>
+      </c>
+      <c r="D21">
+        <v>1546.5755824824523</v>
+      </c>
+      <c r="E21">
+        <v>1510.3537581232913</v>
       </c>
       <c r="F21" t="s">
         <v>69</v>
@@ -2294,79 +2632,79 @@
       <c r="I21" t="s">
         <v>73</v>
       </c>
-      <c r="J21" t="n">
-        <v>312.36342250582493</v>
-      </c>
-      <c r="K21" t="n">
-        <v>9668.528734572054</v>
+      <c r="J21">
+        <v>36.221824359161019</v>
+      </c>
+      <c r="K21">
+        <v>1546.3354147349769</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M21" t="s">
         <v>81</v>
       </c>
-      <c r="N21" t="n">
-        <v>3517.0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>146.97654538453168</v>
-      </c>
-      <c r="R21" t="n">
-        <v>9521.552189187521</v>
+      <c r="N21">
+        <v>570</v>
+      </c>
+      <c r="O21">
+        <v>8</v>
+      </c>
+      <c r="P21">
+        <v>9</v>
+      </c>
+      <c r="Q21">
+        <v>57.110727247457362</v>
+      </c>
+      <c r="R21">
+        <v>1489.2246874875195</v>
       </c>
       <c r="S21" t="s">
-        <v>87</v>
-      </c>
-      <c r="T21" t="n">
-        <v>9263.938785225531</v>
-      </c>
-      <c r="U21" t="n">
-        <v>248.40823809360882</v>
+        <v>98</v>
+      </c>
+      <c r="T21">
+        <v>1528.4646703028718</v>
+      </c>
+      <c r="U21">
+        <v>0.24016774747542513</v>
       </c>
       <c r="V21" t="s">
         <v>125</v>
       </c>
-      <c r="W21" t="n">
-        <v>9544.32461552525</v>
-      </c>
-      <c r="X21" t="n">
-        <v>8960.780528588088</v>
+      <c r="W21">
+        <v>1546.4554986087146</v>
+      </c>
+      <c r="X21">
+        <v>1453.2430308758339</v>
       </c>
       <c r="Y21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4627.366809678576</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>100.0</v>
+        <v>152</v>
+      </c>
+      <c r="Z21">
+        <v>783.73224268537433</v>
+      </c>
+      <c r="AA21">
+        <v>100.03225406474836</v>
       </c>
       <c r="AB21" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
         <v>66</v>
       </c>
-      <c r="D22" t="n">
-        <v>3933.9883883348584</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3842.4863334201277</v>
+      <c r="D22">
+        <v>2127.1665186982655</v>
+      </c>
+      <c r="E22">
+        <v>2070.1836213713696</v>
       </c>
       <c r="F22" t="s">
         <v>69</v>
@@ -2380,11 +2718,11 @@
       <c r="I22" t="s">
         <v>73</v>
       </c>
-      <c r="J22" t="n">
-        <v>91.5020549147307</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4065.2240051185613</v>
+      <c r="J22">
+        <v>56.982897326895909</v>
+      </c>
+      <c r="K22">
+        <v>2139.8094378473497</v>
       </c>
       <c r="L22" t="s">
         <v>77</v>
@@ -2392,67 +2730,67 @@
       <c r="M22" t="s">
         <v>81</v>
       </c>
-      <c r="N22" t="n">
-        <v>1470.0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>65.63715911795504</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3999.5868460006063</v>
+      <c r="N22">
+        <v>810</v>
+      </c>
+      <c r="O22">
+        <v>8</v>
+      </c>
+      <c r="P22">
+        <v>9</v>
+      </c>
+      <c r="Q22">
+        <v>60.27330822899836</v>
+      </c>
+      <c r="R22">
+        <v>2079.5361296183514</v>
       </c>
       <c r="S22" t="s">
-        <v>98</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3888.2373608774933</v>
-      </c>
-      <c r="U22" t="n">
-        <v>131.23561678370288</v>
+        <v>99</v>
+      </c>
+      <c r="T22">
+        <v>2098.6750700348175</v>
+      </c>
+      <c r="U22">
+        <v>12.642919149084264</v>
       </c>
       <c r="V22" t="s">
-        <v>87</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3999.6061967267096</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3776.8491743021727</v>
+        <v>126</v>
+      </c>
+      <c r="W22">
+        <v>2133.4879782728076</v>
+      </c>
+      <c r="X22">
+        <v>2009.9103131423713</v>
       </c>
       <c r="Y22" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1954.0617462690414</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>100.0</v>
+        <v>153</v>
+      </c>
+      <c r="Z22">
+        <v>1065.2284648001839</v>
+      </c>
+      <c r="AA22">
+        <v>100</v>
       </c>
       <c r="AB22" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="n">
-        <v>799.2779927719483</v>
-      </c>
-      <c r="E23" t="n">
-        <v>770.2947954145295</v>
+      <c r="D23">
+        <v>3933.9883883348584</v>
+      </c>
+      <c r="E23">
+        <v>3842.4863334201277</v>
       </c>
       <c r="F23" t="s">
         <v>69</v>
@@ -2466,11 +2804,11 @@
       <c r="I23" t="s">
         <v>73</v>
       </c>
-      <c r="J23" t="n">
-        <v>28.983197357418817</v>
-      </c>
-      <c r="K23" t="n">
-        <v>800.8653736861879</v>
+      <c r="J23">
+        <v>91.502054914730707</v>
+      </c>
+      <c r="K23">
+        <v>4065.2240051185613</v>
       </c>
       <c r="L23" t="s">
         <v>77</v>
@@ -2478,67 +2816,67 @@
       <c r="M23" t="s">
         <v>81</v>
       </c>
-      <c r="N23" t="n">
-        <v>289.0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>50.99784019301189</v>
-      </c>
-      <c r="R23" t="n">
-        <v>749.867533493176</v>
+      <c r="N23">
+        <v>1470</v>
+      </c>
+      <c r="O23">
+        <v>8</v>
+      </c>
+      <c r="P23">
+        <v>9</v>
+      </c>
+      <c r="Q23">
+        <v>65.637159117955036</v>
+      </c>
+      <c r="R23">
+        <v>3999.5868460006063</v>
       </c>
       <c r="S23" t="s">
+        <v>100</v>
+      </c>
+      <c r="T23">
+        <v>3888.2373608774933</v>
+      </c>
+      <c r="U23">
+        <v>131.23561678370288</v>
+      </c>
+      <c r="V23" t="s">
         <v>86</v>
       </c>
-      <c r="T23" t="n">
-        <v>784.7863940932389</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5873809142395885</v>
-      </c>
-      <c r="V23" t="s">
-        <v>126</v>
-      </c>
-      <c r="W23" t="n">
-        <v>800.0716832290682</v>
-      </c>
-      <c r="X23" t="n">
-        <v>719.2969552215176</v>
+      <c r="W23">
+        <v>3999.6061967267096</v>
+      </c>
+      <c r="X23">
+        <v>3776.8491743021727</v>
       </c>
       <c r="Y23" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>410.6463178037707</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>100.0</v>
+        <v>140</v>
+      </c>
+      <c r="Z23">
+        <v>1954.0617462690414</v>
+      </c>
+      <c r="AA23">
+        <v>100</v>
       </c>
       <c r="AB23" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2127.1665186982655</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2070.1836213713696</v>
+        <v>67</v>
+      </c>
+      <c r="D24">
+        <v>9420.1204964784447</v>
+      </c>
+      <c r="E24">
+        <v>9107.7570739726198</v>
       </c>
       <c r="F24" t="s">
         <v>69</v>
@@ -2552,65 +2890,65 @@
       <c r="I24" t="s">
         <v>73</v>
       </c>
-      <c r="J24" t="n">
-        <v>56.98289732689591</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2139.8094378473497</v>
+      <c r="J24">
+        <v>312.36342250582493</v>
+      </c>
+      <c r="K24">
+        <v>9668.5287345720535</v>
       </c>
       <c r="L24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M24" t="s">
         <v>81</v>
       </c>
-      <c r="N24" t="n">
-        <v>810.0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>60.27330822899836</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2079.5361296183514</v>
+      <c r="N24">
+        <v>3517</v>
+      </c>
+      <c r="O24">
+        <v>17</v>
+      </c>
+      <c r="P24">
+        <v>18</v>
+      </c>
+      <c r="Q24">
+        <v>146.97654538453168</v>
+      </c>
+      <c r="R24">
+        <v>9521.5521891875214</v>
       </c>
       <c r="S24" t="s">
-        <v>99</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2098.6750700348175</v>
-      </c>
-      <c r="U24" t="n">
-        <v>12.642919149084264</v>
+        <v>86</v>
+      </c>
+      <c r="T24">
+        <v>9263.9387852255313</v>
+      </c>
+      <c r="U24">
+        <v>248.40823809360882</v>
       </c>
       <c r="V24" t="s">
         <v>127</v>
       </c>
-      <c r="W24" t="n">
-        <v>2133.4879782728076</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2009.9103131423713</v>
+      <c r="W24">
+        <v>9544.3246155252491</v>
+      </c>
+      <c r="X24">
+        <v>8960.7805285880877</v>
       </c>
       <c r="Y24" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1065.228464800184</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>100.0</v>
+        <v>154</v>
+      </c>
+      <c r="Z24">
+        <v>4627.3668096785759</v>
+      </c>
+      <c r="AA24">
+        <v>100</v>
       </c>
       <c r="AB24" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -2620,11 +2958,11 @@
       <c r="C25" t="s">
         <v>66</v>
       </c>
-      <c r="D25" t="n">
-        <v>1546.5755824824523</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1510.3537581232913</v>
+      <c r="D25">
+        <v>9397.2878534613901</v>
+      </c>
+      <c r="E25">
+        <v>9080.7205757217434</v>
       </c>
       <c r="F25" t="s">
         <v>69</v>
@@ -2638,79 +2976,79 @@
       <c r="I25" t="s">
         <v>73</v>
       </c>
-      <c r="J25" t="n">
-        <v>36.22182435916102</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1546.335414734977</v>
+      <c r="J25">
+        <v>316.56727773964667</v>
+      </c>
+      <c r="K25">
+        <v>9668.5287345720535</v>
       </c>
       <c r="L25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M25" t="s">
         <v>81</v>
       </c>
-      <c r="N25" t="n">
-        <v>570.0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>57.11072724745736</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1489.2246874875195</v>
+      <c r="N25">
+        <v>3517</v>
+      </c>
+      <c r="O25">
+        <v>13</v>
+      </c>
+      <c r="P25">
+        <v>14</v>
+      </c>
+      <c r="Q25">
+        <v>114.31509085463574</v>
+      </c>
+      <c r="R25">
+        <v>9554.2136437174177</v>
       </c>
       <c r="S25" t="s">
-        <v>100</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1528.4646703028718</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.24016774747542513</v>
+        <v>86</v>
+      </c>
+      <c r="T25">
+        <v>9239.0042145915668</v>
+      </c>
+      <c r="U25">
+        <v>271.24088111066339</v>
       </c>
       <c r="V25" t="s">
         <v>128</v>
       </c>
-      <c r="W25" t="n">
-        <v>1546.4554986087146</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1453.243030875834</v>
+      <c r="W25">
+        <v>9532.9082940167209</v>
+      </c>
+      <c r="X25">
+        <v>8966.4054848671076</v>
       </c>
       <c r="Y25" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>783.7322426853743</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>100.03225406474836</v>
+        <v>135</v>
+      </c>
+      <c r="Z25">
+        <v>4597.5178332881896</v>
+      </c>
+      <c r="AA25">
+        <v>100</v>
       </c>
       <c r="AB25" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="n">
-        <v>178.9919401377009</v>
-      </c>
-      <c r="E26" t="n">
-        <v>148.0780105157419</v>
+        <v>67</v>
+      </c>
+      <c r="D26">
+        <v>2714.6908857114759</v>
+      </c>
+      <c r="E26">
+        <v>2497.3483821269569</v>
       </c>
       <c r="F26" t="s">
         <v>69</v>
@@ -2724,79 +3062,79 @@
       <c r="I26" t="s">
         <v>73</v>
       </c>
-      <c r="J26" t="n">
-        <v>30.913929621959</v>
-      </c>
-      <c r="K26" t="n">
-        <v>188.4136720396013</v>
+      <c r="J26">
+        <v>217.34250358451891</v>
+      </c>
+      <c r="K26">
+        <v>2937.5105153151762</v>
       </c>
       <c r="L26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M26" t="s">
         <v>81</v>
       </c>
-      <c r="N26" t="n">
-        <v>146.0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>135.6949273049717</v>
-      </c>
-      <c r="R26" t="n">
-        <v>52.71874473462958</v>
+      <c r="N26">
+        <v>3072</v>
+      </c>
+      <c r="O26">
+        <v>17</v>
+      </c>
+      <c r="P26">
+        <v>18</v>
+      </c>
+      <c r="Q26">
+        <v>326.0039051226604</v>
+      </c>
+      <c r="R26">
+        <v>2611.5066101925158</v>
       </c>
       <c r="S26" t="s">
-        <v>101</v>
-      </c>
-      <c r="T26" t="n">
-        <v>163.5349753267214</v>
-      </c>
-      <c r="U26" t="n">
-        <v>9.421731901900387</v>
+        <v>107</v>
+      </c>
+      <c r="T26">
+        <v>2606.0196339192162</v>
+      </c>
+      <c r="U26">
+        <v>222.81962960370038</v>
       </c>
       <c r="V26" t="s">
-        <v>129</v>
-      </c>
-      <c r="W26" t="n">
-        <v>183.7028060886511</v>
-      </c>
-      <c r="X26" t="n">
-        <v>12.383083210770195</v>
+        <v>133</v>
+      </c>
+      <c r="W26">
+        <v>2826.100700513326</v>
+      </c>
+      <c r="X26">
+        <v>2171.3444770042966</v>
       </c>
       <c r="Y26" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>141.88646891035683</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>3531432.4683565227</v>
+        <v>161</v>
+      </c>
+      <c r="Z26">
+        <v>1411.6761436248087</v>
+      </c>
+      <c r="AA26">
+        <v>100</v>
+      </c>
+      <c r="AB26">
+        <v>73392188.364547625</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>66</v>
       </c>
-      <c r="D27" t="n">
-        <v>200.21107646974923</v>
-      </c>
-      <c r="E27" t="n">
-        <v>183.04844091261324</v>
+      <c r="D27">
+        <v>2685.2242910063515</v>
+      </c>
+      <c r="E27">
+        <v>2465.5454203116519</v>
       </c>
       <c r="F27" t="s">
         <v>69</v>
@@ -2810,79 +3148,79 @@
       <c r="I27" t="s">
         <v>73</v>
       </c>
-      <c r="J27" t="n">
-        <v>17.162635557135985</v>
-      </c>
-      <c r="K27" t="n">
-        <v>207.09546233829298</v>
+      <c r="J27">
+        <v>219.67887069469953</v>
+      </c>
+      <c r="K27">
+        <v>2937.5105153151762</v>
       </c>
       <c r="L27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M27" t="s">
         <v>81</v>
       </c>
-      <c r="N27" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>130.94845580906312</v>
-      </c>
-      <c r="R27" t="n">
-        <v>76.14700652922986</v>
+      <c r="N27">
+        <v>3072</v>
+      </c>
+      <c r="O27">
+        <v>13</v>
+      </c>
+      <c r="P27">
+        <v>14</v>
+      </c>
+      <c r="Q27">
+        <v>253.55859287318029</v>
+      </c>
+      <c r="R27">
+        <v>2683.951922441996</v>
       </c>
       <c r="S27" t="s">
-        <v>102</v>
-      </c>
-      <c r="T27" t="n">
-        <v>191.62975869118122</v>
-      </c>
-      <c r="U27" t="n">
-        <v>6.884385868543745</v>
+        <v>108</v>
+      </c>
+      <c r="T27">
+        <v>2575.3848556590019</v>
+      </c>
+      <c r="U27">
+        <v>252.28622430882479</v>
       </c>
       <c r="V27" t="s">
-        <v>130</v>
-      </c>
-      <c r="W27" t="n">
-        <v>203.6532694040211</v>
-      </c>
-      <c r="X27" t="n">
-        <v>52.099985103550125</v>
+        <v>93</v>
+      </c>
+      <c r="W27">
+        <v>2811.3674031607638</v>
+      </c>
+      <c r="X27">
+        <v>2211.9868274384717</v>
       </c>
       <c r="Y27" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>156.99844836083818</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2084059.897883856</v>
+        <v>162</v>
+      </c>
+      <c r="Z27">
+        <v>1359.5520065924161</v>
+      </c>
+      <c r="AA27">
+        <v>100</v>
+      </c>
+      <c r="AB27">
+        <v>73392188.364547625</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
         <v>66</v>
       </c>
-      <c r="D28" t="n">
-        <v>247.0502201807476</v>
-      </c>
-      <c r="E28" t="n">
-        <v>233.270613334038</v>
+      <c r="D28">
+        <v>417.21401118690414</v>
+      </c>
+      <c r="E28">
+        <v>388.10970711771722</v>
       </c>
       <c r="F28" t="s">
         <v>69</v>
@@ -2896,11 +3234,11 @@
       <c r="I28" t="s">
         <v>73</v>
       </c>
-      <c r="J28" t="n">
-        <v>13.779606846709612</v>
-      </c>
-      <c r="K28" t="n">
-        <v>255.81621406346676</v>
+      <c r="J28">
+        <v>29.104304069186924</v>
+      </c>
+      <c r="K28">
+        <v>417.39598867452742</v>
       </c>
       <c r="L28" t="s">
         <v>77</v>
@@ -2908,67 +3246,67 @@
       <c r="M28" t="s">
         <v>81</v>
       </c>
-      <c r="N28" t="n">
-        <v>265.0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>137.79565508344953</v>
-      </c>
-      <c r="R28" t="n">
-        <v>118.02055898001723</v>
+      <c r="N28">
+        <v>479</v>
+      </c>
+      <c r="O28">
+        <v>8</v>
+      </c>
+      <c r="P28">
+        <v>9</v>
+      </c>
+      <c r="Q28">
+        <v>140.62213718389924</v>
+      </c>
+      <c r="R28">
+        <v>276.7738514906282</v>
       </c>
       <c r="S28" t="s">
-        <v>103</v>
-      </c>
-      <c r="T28" t="n">
-        <v>240.1604167573928</v>
-      </c>
-      <c r="U28" t="n">
-        <v>8.765993882719158</v>
+        <v>104</v>
+      </c>
+      <c r="T28">
+        <v>402.66185915231068</v>
+      </c>
+      <c r="U28">
+        <v>0.18197748762327137</v>
       </c>
       <c r="V28" t="s">
-        <v>131</v>
-      </c>
-      <c r="W28" t="n">
-        <v>251.43321712210718</v>
-      </c>
-      <c r="X28" t="n">
-        <v>95.47495825058846</v>
+        <v>112</v>
+      </c>
+      <c r="W28">
+        <v>417.30499993071578</v>
+      </c>
+      <c r="X28">
+        <v>247.48756993381798</v>
       </c>
       <c r="Y28" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>185.53313420874377</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>4459861.825137717</v>
+        <v>158</v>
+      </c>
+      <c r="Z28">
+        <v>264.36592215080822</v>
+      </c>
+      <c r="AA28">
+        <v>100</v>
+      </c>
+      <c r="AB28">
+        <v>6105386.11557924</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
-      <c r="D29" t="n">
-        <v>2685.2242910063515</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2465.545420311652</v>
+      <c r="D29">
+        <v>200.21107646974923</v>
+      </c>
+      <c r="E29">
+        <v>183.04844091261324</v>
       </c>
       <c r="F29" t="s">
         <v>69</v>
@@ -2982,79 +3320,79 @@
       <c r="I29" t="s">
         <v>73</v>
       </c>
-      <c r="J29" t="n">
-        <v>219.67887069469953</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2937.5105153151762</v>
+      <c r="J29">
+        <v>17.162635557135985</v>
+      </c>
+      <c r="K29">
+        <v>207.09546233829298</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M29" t="s">
         <v>81</v>
       </c>
-      <c r="N29" t="n">
-        <v>3072.0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>253.5585928731803</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2683.951922441996</v>
+      <c r="N29">
+        <v>210</v>
+      </c>
+      <c r="O29">
+        <v>8</v>
+      </c>
+      <c r="P29">
+        <v>9</v>
+      </c>
+      <c r="Q29">
+        <v>130.94845580906312</v>
+      </c>
+      <c r="R29">
+        <v>76.147006529229856</v>
       </c>
       <c r="S29" t="s">
-        <v>104</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2575.384855659002</v>
-      </c>
-      <c r="U29" t="n">
-        <v>252.28622430882479</v>
+        <v>102</v>
+      </c>
+      <c r="T29">
+        <v>191.62975869118122</v>
+      </c>
+      <c r="U29">
+        <v>6.8843858685437453</v>
       </c>
       <c r="V29" t="s">
-        <v>96</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2811.367403160764</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2211.9868274384717</v>
+        <v>130</v>
+      </c>
+      <c r="W29">
+        <v>203.6532694040211</v>
+      </c>
+      <c r="X29">
+        <v>52.099985103550125</v>
       </c>
       <c r="Y29" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1359.552006592416</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>7.339218836454763E7</v>
+        <v>156</v>
+      </c>
+      <c r="Z29">
+        <v>156.99844836083818</v>
+      </c>
+      <c r="AA29">
+        <v>100</v>
+      </c>
+      <c r="AB29">
+        <v>2084059.897883856</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
         <v>66</v>
       </c>
-      <c r="D30" t="n">
-        <v>1123.3428664170335</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1051.7317613296723</v>
+      <c r="D30">
+        <v>580.61887032120251</v>
+      </c>
+      <c r="E30">
+        <v>545.06848955497048</v>
       </c>
       <c r="F30" t="s">
         <v>69</v>
@@ -3068,11 +3406,11 @@
       <c r="I30" t="s">
         <v>73</v>
       </c>
-      <c r="J30" t="n">
-        <v>71.61110508736124</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1236.4523942074045</v>
+      <c r="J30">
+        <v>35.550380766232024</v>
+      </c>
+      <c r="K30">
+        <v>588.86174422475676</v>
       </c>
       <c r="L30" t="s">
         <v>77</v>
@@ -3080,67 +3418,67 @@
       <c r="M30" t="s">
         <v>81</v>
       </c>
-      <c r="N30" t="n">
-        <v>1269.0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>159.10754709662973</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1077.3448471107747</v>
+      <c r="N30">
+        <v>703</v>
+      </c>
+      <c r="O30">
+        <v>8</v>
+      </c>
+      <c r="P30">
+        <v>9</v>
+      </c>
+      <c r="Q30">
+        <v>144.69400994652517</v>
+      </c>
+      <c r="R30">
+        <v>444.16773427823159</v>
       </c>
       <c r="S30" t="s">
         <v>105</v>
       </c>
-      <c r="T30" t="n">
-        <v>1087.537313873353</v>
-      </c>
-      <c r="U30" t="n">
-        <v>113.10952779037098</v>
+      <c r="T30">
+        <v>562.84367993808655</v>
+      </c>
+      <c r="U30">
+        <v>8.2428739035542549</v>
       </c>
       <c r="V30" t="s">
-        <v>107</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1179.897630312219</v>
-      </c>
-      <c r="X30" t="n">
-        <v>892.6242142330425</v>
+        <v>132</v>
+      </c>
+      <c r="W30">
+        <v>584.74030727297963</v>
+      </c>
+      <c r="X30">
+        <v>400.37447960844531</v>
       </c>
       <c r="Y30" t="s">
         <v>159</v>
       </c>
-      <c r="Z30" t="n">
-        <v>605.419654213151</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>4.761299775800688E7</v>
+      <c r="Z30">
+        <v>344.88124975074783</v>
+      </c>
+      <c r="AA30">
+        <v>100</v>
+      </c>
+      <c r="AB30">
+        <v>9598450.2995834183</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2714.690885711476</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2497.348382126957</v>
+        <v>66</v>
+      </c>
+      <c r="D31">
+        <v>1123.3428664170335</v>
+      </c>
+      <c r="E31">
+        <v>1051.7317613296723</v>
       </c>
       <c r="F31" t="s">
         <v>69</v>
@@ -3154,79 +3492,79 @@
       <c r="I31" t="s">
         <v>73</v>
       </c>
-      <c r="J31" t="n">
-        <v>217.3425035845189</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2937.5105153151762</v>
+      <c r="J31">
+        <v>71.611105087361238</v>
+      </c>
+      <c r="K31">
+        <v>1236.4523942074045</v>
       </c>
       <c r="L31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M31" t="s">
         <v>81</v>
       </c>
-      <c r="N31" t="n">
-        <v>3072.0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>326.0039051226604</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2611.506610192516</v>
+      <c r="N31">
+        <v>1269</v>
+      </c>
+      <c r="O31">
+        <v>8</v>
+      </c>
+      <c r="P31">
+        <v>9</v>
+      </c>
+      <c r="Q31">
+        <v>159.10754709662973</v>
+      </c>
+      <c r="R31">
+        <v>1077.3448471107747</v>
       </c>
       <c r="S31" t="s">
         <v>106</v>
       </c>
-      <c r="T31" t="n">
-        <v>2606.019633919216</v>
-      </c>
-      <c r="U31" t="n">
-        <v>222.81962960370038</v>
+      <c r="T31">
+        <v>1087.537313873353</v>
+      </c>
+      <c r="U31">
+        <v>113.10952779037098</v>
       </c>
       <c r="V31" t="s">
-        <v>132</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2826.100700513326</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2171.3444770042966</v>
+        <v>104</v>
+      </c>
+      <c r="W31">
+        <v>1179.897630312219</v>
+      </c>
+      <c r="X31">
+        <v>892.62421423304249</v>
       </c>
       <c r="Y31" t="s">
         <v>160</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1411.6761436248087</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>7.339218836454763E7</v>
+      <c r="Z31">
+        <v>605.41965421315103</v>
+      </c>
+      <c r="AA31">
+        <v>100</v>
+      </c>
+      <c r="AB31">
+        <v>47612997.758006878</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
         <v>66</v>
       </c>
-      <c r="D32" t="n">
-        <v>417.21401118690414</v>
-      </c>
-      <c r="E32" t="n">
-        <v>388.1097071177172</v>
+      <c r="D32">
+        <v>247.0502201807476</v>
+      </c>
+      <c r="E32">
+        <v>233.27061333403799</v>
       </c>
       <c r="F32" t="s">
         <v>69</v>
@@ -3240,11 +3578,11 @@
       <c r="I32" t="s">
         <v>73</v>
       </c>
-      <c r="J32" t="n">
-        <v>29.104304069186924</v>
-      </c>
-      <c r="K32" t="n">
-        <v>417.3959886745274</v>
+      <c r="J32">
+        <v>13.779606846709612</v>
+      </c>
+      <c r="K32">
+        <v>255.81621406346676</v>
       </c>
       <c r="L32" t="s">
         <v>77</v>
@@ -3252,67 +3590,67 @@
       <c r="M32" t="s">
         <v>81</v>
       </c>
-      <c r="N32" t="n">
-        <v>479.0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>140.62213718389924</v>
-      </c>
-      <c r="R32" t="n">
-        <v>276.7738514906282</v>
+      <c r="N32">
+        <v>265</v>
+      </c>
+      <c r="O32">
+        <v>8</v>
+      </c>
+      <c r="P32">
+        <v>9</v>
+      </c>
+      <c r="Q32">
+        <v>137.79565508344953</v>
+      </c>
+      <c r="R32">
+        <v>118.02055898001723</v>
       </c>
       <c r="S32" t="s">
-        <v>107</v>
-      </c>
-      <c r="T32" t="n">
-        <v>402.6618591523107</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.18197748762327137</v>
+        <v>103</v>
+      </c>
+      <c r="T32">
+        <v>240.1604167573928</v>
+      </c>
+      <c r="U32">
+        <v>8.7659938827191581</v>
       </c>
       <c r="V32" t="s">
-        <v>114</v>
-      </c>
-      <c r="W32" t="n">
-        <v>417.3049999307158</v>
-      </c>
-      <c r="X32" t="n">
-        <v>247.48756993381798</v>
+        <v>131</v>
+      </c>
+      <c r="W32">
+        <v>251.43321712210718</v>
+      </c>
+      <c r="X32">
+        <v>95.474958250588458</v>
       </c>
       <c r="Y32" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>264.3659221508082</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>6105386.11557924</v>
+        <v>157</v>
+      </c>
+      <c r="Z32">
+        <v>185.53313420874377</v>
+      </c>
+      <c r="AA32">
+        <v>100</v>
+      </c>
+      <c r="AB32">
+        <v>4459861.8251377167</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
         <v>66</v>
       </c>
-      <c r="D33" t="n">
-        <v>580.6188703212025</v>
-      </c>
-      <c r="E33" t="n">
-        <v>545.0684895549705</v>
+      <c r="D33">
+        <v>178.99194013770091</v>
+      </c>
+      <c r="E33">
+        <v>148.07801051574191</v>
       </c>
       <c r="F33" t="s">
         <v>69</v>
@@ -3326,11 +3664,11 @@
       <c r="I33" t="s">
         <v>73</v>
       </c>
-      <c r="J33" t="n">
-        <v>35.550380766232024</v>
-      </c>
-      <c r="K33" t="n">
-        <v>588.8617442247568</v>
+      <c r="J33">
+        <v>30.913929621958999</v>
+      </c>
+      <c r="K33">
+        <v>188.41367203960129</v>
       </c>
       <c r="L33" t="s">
         <v>77</v>
@@ -3338,53 +3676,68 @@
       <c r="M33" t="s">
         <v>81</v>
       </c>
-      <c r="N33" t="n">
-        <v>703.0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>144.69400994652517</v>
-      </c>
-      <c r="R33" t="n">
-        <v>444.1677342782316</v>
+      <c r="N33">
+        <v>146</v>
+      </c>
+      <c r="O33">
+        <v>8</v>
+      </c>
+      <c r="P33">
+        <v>9</v>
+      </c>
+      <c r="Q33">
+        <v>135.69492730497171</v>
+      </c>
+      <c r="R33">
+        <v>52.718744734629581</v>
       </c>
       <c r="S33" t="s">
-        <v>108</v>
-      </c>
-      <c r="T33" t="n">
-        <v>562.8436799380866</v>
-      </c>
-      <c r="U33" t="n">
-        <v>8.242873903554255</v>
+        <v>101</v>
+      </c>
+      <c r="T33">
+        <v>163.53497532672139</v>
+      </c>
+      <c r="U33">
+        <v>9.4217319019003867</v>
       </c>
       <c r="V33" t="s">
-        <v>133</v>
-      </c>
-      <c r="W33" t="n">
-        <v>584.7403072729796</v>
-      </c>
-      <c r="X33" t="n">
-        <v>400.3744796084453</v>
+        <v>129</v>
+      </c>
+      <c r="W33">
+        <v>183.7028060886511</v>
+      </c>
+      <c r="X33">
+        <v>12.383083210770195</v>
       </c>
       <c r="Y33" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>344.8812497507478</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>9598450.299583418</v>
+        <v>155</v>
+      </c>
+      <c r="Z33">
+        <v>141.88646891035683</v>
+      </c>
+      <c r="AA33">
+        <v>100</v>
+      </c>
+      <c r="AB33">
+        <v>3531432.4683565227</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:AB33" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + INDFMPIR"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="weighted"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:AB33">
+      <sortCondition ref="B1:B33"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>